--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>98.1064016771641</v>
+        <v>15.94229027253917</v>
       </c>
       <c r="D2" t="n">
-        <v>99.15334826718629</v>
+        <v>16.11241909341777</v>
       </c>
       <c r="E2" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F2" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>111.5537396278499</v>
+        <v>18.12748268952561</v>
       </c>
       <c r="D3" t="n">
-        <v>112.6361985584169</v>
+        <v>18.30338226574275</v>
       </c>
       <c r="E3" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F3" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.534968473555561</v>
+        <v>1.061932376952779</v>
       </c>
       <c r="D4" t="n">
-        <v>3.040825208811635</v>
+        <v>0.4941340964318908</v>
       </c>
       <c r="E4" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F4" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.357731891969461</v>
+        <v>1.195631432445037</v>
       </c>
       <c r="D5" t="n">
-        <v>10.61839431894282</v>
+        <v>1.725489076828208</v>
       </c>
       <c r="E5" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F5" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.73341480317323</v>
+        <v>2.719179905515649</v>
       </c>
       <c r="D6" t="n">
-        <v>19.80045429327946</v>
+        <v>3.217573822657912</v>
       </c>
       <c r="E6" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F6" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.42720279848275</v>
+        <v>5.106920454753448</v>
       </c>
       <c r="D7" t="n">
-        <v>34.5969664022345</v>
+        <v>5.622007040363107</v>
       </c>
       <c r="E7" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F7" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.21450093099735</v>
+        <v>7.34735640128707</v>
       </c>
       <c r="D8" t="n">
-        <v>45.3431480650065</v>
+        <v>7.368261560563556</v>
       </c>
       <c r="E8" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F8" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.22519853602119</v>
+        <v>3.774094762103443</v>
       </c>
       <c r="D9" t="n">
-        <v>22.69003540067761</v>
+        <v>3.687130752610111</v>
       </c>
       <c r="E9" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F9" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.75200793438032</v>
+        <v>8.734701289336803</v>
       </c>
       <c r="D10" t="n">
-        <v>52.79737211630115</v>
+        <v>8.579572968898937</v>
       </c>
       <c r="E10" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F10" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.08296619912242</v>
+        <v>3.913482007357394</v>
       </c>
       <c r="D11" t="n">
-        <v>24.1453768233205</v>
+        <v>3.923623733789581</v>
       </c>
       <c r="E11" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F11" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>79.11561668833136</v>
+        <v>12.85628771185385</v>
       </c>
       <c r="D12" t="n">
-        <v>78.0394496523293</v>
+        <v>12.68141056850351</v>
       </c>
       <c r="E12" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F12" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63.01615544903913</v>
+        <v>10.24012526046886</v>
       </c>
       <c r="D13" t="n">
-        <v>58.4731716001635</v>
+        <v>9.501890385026568</v>
       </c>
       <c r="E13" t="n">
-        <v>33.63088944519804</v>
+        <v>5.465019534844682</v>
       </c>
       <c r="F13" t="n">
-        <v>33.44387724382121</v>
+        <v>5.434630052120947</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
